--- a/testdata/configurationUAT/data.xlsx
+++ b/testdata/configurationUAT/data.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15503" windowHeight="8964"/>
+    <workbookView windowWidth="22944" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="115">
   <si>
     <t>username</t>
   </si>
@@ -173,6 +173,24 @@
     <t>auth_personal_account_owner_name</t>
   </si>
   <si>
+    <t>auth_savings_account_number</t>
+  </si>
+  <si>
+    <t>auth_savings_account_name</t>
+  </si>
+  <si>
+    <t>fee_clean_RSD</t>
+  </si>
+  <si>
+    <t>fee_with_NBSP_RSD</t>
+  </si>
+  <si>
+    <t>fee_clean_EUR</t>
+  </si>
+  <si>
+    <t>fee_with_NBSP_EUR</t>
+  </si>
+  <si>
     <t>Osir ANOEV</t>
   </si>
   <si>
@@ -212,6 +230,9 @@
     <t>205-9001001027335-67</t>
   </si>
   <si>
+    <t>205-9001033138759-84</t>
+  </si>
+  <si>
     <t>205900100102733567</t>
   </si>
   <si>
@@ -236,16 +257,16 @@
     <t>Naknada za TR</t>
   </si>
   <si>
+    <t>Visa prepaid</t>
+  </si>
+  <si>
+    <t>4313 **** **** 0619</t>
+  </si>
+  <si>
     <t>Visa revolving card</t>
   </si>
   <si>
-    <t>4176 **** **** 2688</t>
-  </si>
-  <si>
-    <t>Visa prepaid</t>
-  </si>
-  <si>
-    <t>4313 **** **** 5309</t>
+    <t>4176 **** **** 6236</t>
   </si>
   <si>
     <t>0049034095794</t>
@@ -299,6 +320,21 @@
     <t>MILENKA AĆIMOVIĆ</t>
   </si>
   <si>
+    <t>9011009711346</t>
+  </si>
+  <si>
+    <t>A vista depozitni račun HAJRIJA LOVRIĆ</t>
+  </si>
+  <si>
+    <t>15,00 RSD</t>
+  </si>
+  <si>
+    <t>15,00 RSD</t>
+  </si>
+  <si>
+    <t>0,00 EUR</t>
+  </si>
+  <si>
     <t>Enil ČIĆVI</t>
   </si>
   <si>
@@ -333,6 +369,9 @@
   </si>
   <si>
     <t>15. 1. 2032</t>
+  </si>
+  <si>
+    <t>0,00 EUR</t>
   </si>
 </sst>
 </file>
@@ -1331,7 +1370,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AV9"/>
+  <dimension ref="A1:BB9"/>
   <sheetFormatPr defaultColWidth="8.87962962962963" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.75" customWidth="1"/>
@@ -1356,8 +1395,12 @@
     <col min="22" max="22" width="22.8888888888889" customWidth="1"/>
     <col min="23" max="23" width="24.6666666666667" customWidth="1"/>
     <col min="24" max="24" width="22.8888888888889" customWidth="1"/>
-    <col min="25" max="26" width="24.6666666666667" customWidth="1"/>
-    <col min="27" max="30" width="33.2222222222222" customWidth="1"/>
+    <col min="25" max="25" width="24.6666666666667" customWidth="1"/>
+    <col min="26" max="26" width="15.1111111111111" customWidth="1"/>
+    <col min="27" max="27" width="17.6666666666667" customWidth="1"/>
+    <col min="28" max="28" width="20.1111111111111" customWidth="1"/>
+    <col min="29" max="29" width="19.5555555555556" customWidth="1"/>
+    <col min="30" max="30" width="33.2222222222222" customWidth="1"/>
     <col min="31" max="31" width="21.2222222222222" customWidth="1"/>
     <col min="32" max="32" width="19.4444444444444" customWidth="1"/>
     <col min="33" max="33" width="22.4444444444444" customWidth="1"/>
@@ -1374,9 +1417,15 @@
     <col min="46" max="46" width="27.8888888888889" customWidth="1"/>
     <col min="47" max="47" width="27.2222222222222" customWidth="1"/>
     <col min="48" max="48" width="35.5555555555556" customWidth="1"/>
+    <col min="49" max="49" width="29" customWidth="1"/>
+    <col min="50" max="50" width="36.2222222222222" customWidth="1"/>
+    <col min="51" max="51" width="14.4444444444444" customWidth="1"/>
+    <col min="52" max="52" width="19.5555555555556" customWidth="1"/>
+    <col min="53" max="53" width="14.6666666666667" customWidth="1"/>
+    <col min="54" max="54" width="19.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:48">
+    <row r="1" customFormat="1" spans="1:54">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1521,1186 +1570,1338 @@
       <c r="AV1" t="s">
         <v>47</v>
       </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="2" customFormat="1" spans="1:48">
+    <row r="2" customFormat="1" spans="1:54">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="I2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG2" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI2" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK2" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM2" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW2" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>100</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="1:54">
+      <c r="A3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="E3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="F3" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="H3" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="I3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y3" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC3" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE3" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG3" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI3" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK3" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM3" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW3" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>100</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>101</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:54">
+      <c r="A4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="F4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="U2" s="1" t="s">
+      <c r="J4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="V2" s="9" t="s">
+      <c r="N4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="O4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="X2" s="9" t="s">
+      <c r="P4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="R4" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC4" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE4" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG4" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI4" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK4" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM4" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>93</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>95</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW4" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>99</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>100</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>101</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:54">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="Z2" s="6" t="s">
+      <c r="P5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R5" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="S5" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="T5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AC2" s="6" t="s">
+      <c r="U5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="V5" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="AE2" s="7" t="s">
+      <c r="W5" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="X5" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="AG2" s="7" t="s">
+      <c r="Y5" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z5" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AA5" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="AI2" s="10" t="s">
+      <c r="AB5" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AJ2" s="10" t="s">
+      <c r="AC5" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="AK2" s="10" t="s">
+      <c r="AD5" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AE5" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AM2" s="10" t="s">
+      <c r="AF5" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AG5" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AH5" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AI5" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK5" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM5" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>89</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>94</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW5" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>98</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>100</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>101</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:54">
+      <c r="A6" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="V6" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="W6" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="X6" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y6" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA6" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE6" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG6" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH6" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AI6" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AJ6" t="s">
         <v>85</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AK6" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AL6" t="s">
         <v>87</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AM6" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AN6" t="s">
         <v>89</v>
       </c>
+      <c r="AO6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>95</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW6" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>100</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>101</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>101</v>
+      </c>
     </row>
-    <row r="3" customFormat="1" spans="1:48">
-      <c r="A3" s="1" t="s">
+    <row r="7" s="1" customFormat="1" spans="1:54">
+      <c r="A7" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="V7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="W7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="X7" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC7" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE7" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG7" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI7" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK7" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM7" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AO7" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" s="7" t="s">
+      <c r="AP7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>93</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>94</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>95</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW7" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>99</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>100</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>101</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:54">
+      <c r="A8" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="C8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="V8" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="W8" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="X8" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y8" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC8" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG8" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI8" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK8" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM8" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ8" t="s">
         <v>91</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="AR8" t="s">
         <v>92</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="AS8" t="s">
+        <v>93</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>94</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>95</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>98</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>99</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>100</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>101</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:54">
+      <c r="A9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="F9" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="G9" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="H9" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="Q3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R3" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="S3" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="U3" s="1" t="s">
+      <c r="J9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="N9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="O9" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="P9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="Y3" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z3" s="6" t="s">
+      <c r="R9" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="S9" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="T9" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AC3" s="6" t="s">
+      <c r="U9" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AD3" s="1" t="s">
+      <c r="V9" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="AE3" s="7" t="s">
+      <c r="W9" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AF3" s="1" t="s">
+      <c r="X9" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="AG3" s="7" t="s">
+      <c r="Y9" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z9" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="AH3" s="1" t="s">
+      <c r="AA9" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="AI3" s="10" t="s">
+      <c r="AB9" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AJ3" s="10" t="s">
+      <c r="AC9" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="AK3" s="10" t="s">
+      <c r="AD9" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AE9" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="AM3" s="10" t="s">
+      <c r="AF9" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="AN3" t="s">
+      <c r="AG9" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="AO3" t="s">
+      <c r="AH9" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AP3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AQ3" t="s">
+      <c r="AI9" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="AJ9" t="s">
         <v>85</v>
       </c>
-      <c r="AS3" t="s">
+      <c r="AK9" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="AT3" t="s">
+      <c r="AL9" t="s">
         <v>87</v>
       </c>
-      <c r="AU3" t="s">
+      <c r="AM9" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="AV3" t="s">
+      <c r="AN9" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="4" customFormat="1" spans="1:48">
-      <c r="A4" s="1" t="s">
+      <c r="AO9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>91</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS9" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="AT9" t="s">
         <v>94</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="AU9" t="s">
         <v>95</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="V4" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="W4" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="X4" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y4" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z4" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC4" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AE4" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG4" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH4" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI4" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ4" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK4" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM4" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>82</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>88</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:48">
-      <c r="A5" t="s">
+      <c r="AV9" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="AW9" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="AX9" t="s">
         <v>98</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="V5" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="W5" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="X5" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y5" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z5" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA5" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB5" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC5" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AE5" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG5" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH5" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI5" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ5" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK5" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM5" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:48">
-      <c r="A6" s="1" t="s">
+      <c r="AY9" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="AZ9" t="s">
         <v>100</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="BA9" t="s">
         <v>101</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R6" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="V6" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="W6" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="X6" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y6" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z6" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC6" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AE6" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF6" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG6" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI6" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ6" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK6" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM6" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>82</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>86</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:48">
-      <c r="A7" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="V7" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="W7" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="X7" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y7" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z7" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB7" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC7" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AE7" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG7" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH7" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI7" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ7" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK7" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM7" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>83</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>83</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>85</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>86</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>88</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:48">
-      <c r="A8" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="V8" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="W8" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="X8" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y8" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z8" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB8" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC8" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AE8" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF8" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG8" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI8" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ8" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK8" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL8" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM8" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN8" t="s">
-        <v>82</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>83</v>
-      </c>
-      <c r="AP8" t="s">
-        <v>83</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>85</v>
-      </c>
-      <c r="AS8" t="s">
-        <v>86</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>88</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:48">
-      <c r="A9" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="R9" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="V9" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="W9" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="X9" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y9" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z9" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA9" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB9" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC9" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AE9" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG9" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH9" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI9" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ9" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK9" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM9" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>82</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>85</v>
-      </c>
-      <c r="AS9" t="s">
-        <v>86</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU9" t="s">
-        <v>88</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>89</v>
+      <c r="BB9" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
-    <hyperlink ref="B3" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
-    <hyperlink ref="B4" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
-    <hyperlink ref="B5" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
-    <hyperlink ref="B6" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
-    <hyperlink ref="B7" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
-    <hyperlink ref="B8" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
-    <hyperlink ref="B9" r:id="rId1" display="https://uat.dbp.nlb.si/web-retail/login" tooltip="https://uat.dbp.nlb.si/web-retail/login"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
